--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.19328609937466</v>
+        <v>4.256408991148382</v>
       </c>
       <c r="D2" t="n">
-        <v>26.6149086423968</v>
+        <v>4.32492265438948</v>
       </c>
       <c r="E2" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F2" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.1394560507463</v>
+        <v>4.085161608246275</v>
       </c>
       <c r="D3" t="n">
-        <v>24.94719332703642</v>
+        <v>4.053918915643418</v>
       </c>
       <c r="E3" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F3" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.01070157394894</v>
+        <v>6.501739005766703</v>
       </c>
       <c r="D4" t="n">
-        <v>37.76356093365595</v>
+        <v>6.136578651719091</v>
       </c>
       <c r="E4" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F4" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.25619977888554</v>
+        <v>6.8666324640689</v>
       </c>
       <c r="D5" t="n">
-        <v>37.32520563486323</v>
+        <v>6.065345915665275</v>
       </c>
       <c r="E5" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F5" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.73474634849512</v>
+        <v>7.269396281630457</v>
       </c>
       <c r="D6" t="n">
-        <v>22.77126752747051</v>
+        <v>3.700330973213958</v>
       </c>
       <c r="E6" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F6" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.24202526433093</v>
+        <v>8.814329105453776</v>
       </c>
       <c r="D7" t="n">
-        <v>51.10967499253788</v>
+        <v>8.305322186287405</v>
       </c>
       <c r="E7" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F7" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.73653627659957</v>
+        <v>3.20718714494743</v>
       </c>
       <c r="D8" t="n">
-        <v>19.233538736948</v>
+        <v>3.125450044754049</v>
       </c>
       <c r="E8" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F8" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.29583511443719</v>
+        <v>5.248073206096043</v>
       </c>
       <c r="D9" t="n">
-        <v>17.14621200726474</v>
+        <v>2.78625945118052</v>
       </c>
       <c r="E9" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F9" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.06037504783341</v>
+        <v>5.047310945272929</v>
       </c>
       <c r="D10" t="n">
-        <v>18.33177290363703</v>
+        <v>2.978913096841018</v>
       </c>
       <c r="E10" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F10" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.11233670549785</v>
+        <v>6.193254714643401</v>
       </c>
       <c r="D11" t="n">
-        <v>38.02778816879021</v>
+        <v>6.179515577428409</v>
       </c>
       <c r="E11" t="n">
-        <v>9.907734701365577</v>
+        <v>1.610006888971906</v>
       </c>
       <c r="F11" t="n">
-        <v>10.61129515090711</v>
+        <v>1.724335462022405</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
